--- a/exports/trend_1d/LICI_full_report.xlsx
+++ b/exports/trend_1d/LICI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>8.26</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44719</v>
+        <v>44720</v>
       </c>
       <c r="H2" t="n">
-        <v>367.9</v>
+        <v>360.55</v>
       </c>
       <c r="I2" t="n">
         <v>363.625</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>-7.18</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>7.33</v>
+        <v>9.27</v>
       </c>
       <c r="M2" t="n">
         <v>3.32</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.55</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44754</v>
+        <v>44755</v>
       </c>
       <c r="H3" t="n">
-        <v>350.6</v>
+        <v>351.15</v>
       </c>
       <c r="I3" t="n">
         <v>350.9506216556784</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K3" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="L3" t="n">
         <v>2.02</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>6.64</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H4" t="n">
-        <v>331.65</v>
+        <v>327.4</v>
       </c>
       <c r="I4" t="n">
         <v>327.8296524889178</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.55</v>
+        <v>-6.76</v>
       </c>
       <c r="L4" t="n">
-        <v>6.76</v>
+        <v>7.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="N4" t="n">
         <v>1.7</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>4.78</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44866</v>
+        <v>44867</v>
       </c>
       <c r="H5" t="n">
-        <v>295.65</v>
+        <v>302.6</v>
       </c>
       <c r="I5" t="n">
         <v>301.6997423005091</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
-        <v>9.699999999999999</v>
+        <v>7.57</v>
       </c>
       <c r="L5" t="n">
         <v>1.18</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.92</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44886</v>
+        <v>44887</v>
       </c>
       <c r="H6" t="n">
-        <v>306.3</v>
+        <v>305.75</v>
       </c>
       <c r="I6" t="n">
         <v>305.8610267762115</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="L6" t="n">
         <v>2.63</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>7.34</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H7" t="n">
-        <v>323.6</v>
+        <v>328.2</v>
       </c>
       <c r="I7" t="n">
         <v>325.273748972121</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.84</v>
+        <v>-7.34</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>0.51</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>5.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H8" t="n">
-        <v>333</v>
+        <v>321.85</v>
       </c>
       <c r="I8" t="n">
         <v>331.2415214192044</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>1.46</v>
+        <v>-1.93</v>
       </c>
       <c r="L8" t="n">
-        <v>1.16</v>
+        <v>2.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45065</v>
+        <v>45068</v>
       </c>
       <c r="H9" t="n">
-        <v>276.05</v>
+        <v>282.15</v>
       </c>
       <c r="I9" t="n">
         <v>280.0106440708387</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K9" t="n">
-        <v>14.23</v>
+        <v>12.33</v>
       </c>
       <c r="L9" t="n">
         <v>13.24</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45202</v>
+        <v>45203</v>
       </c>
       <c r="H10" t="n">
-        <v>315.3</v>
+        <v>311.4</v>
       </c>
       <c r="I10" t="n">
         <v>313.6639140293101</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K10" t="n">
-        <v>11.75</v>
+        <v>10.37</v>
       </c>
       <c r="L10" t="n">
         <v>1.88</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>4.76</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="H11" t="n">
-        <v>301.8</v>
+        <v>331.05</v>
       </c>
       <c r="I11" t="n">
         <v>305.714244929651</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K11" t="n">
-        <v>3.08</v>
+        <v>-6.31</v>
       </c>
       <c r="L11" t="n">
-        <v>2.26</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
         <v>0.63</v>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>9.69</v>
       </c>
       <c r="O11" t="n">
         <v>-1.24</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.14</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H12" t="n">
-        <v>481.8</v>
+        <v>444.5</v>
       </c>
       <c r="I12" t="n">
         <v>474.828716201542</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K12" t="n">
-        <v>45.54</v>
+        <v>34.27</v>
       </c>
       <c r="L12" t="n">
         <v>8.41</v>
@@ -1125,7 +1268,7 @@
         <v>1.19</v>
       </c>
       <c r="N12" t="n">
-        <v>6.57</v>
+        <v>7.74</v>
       </c>
       <c r="O12" t="n">
         <v>9.69</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>17.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="H13" t="n">
-        <v>487.45</v>
+        <v>491.75</v>
       </c>
       <c r="I13" t="n">
         <v>491.1067887753778</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.66</v>
+        <v>-10.63</v>
       </c>
       <c r="L13" t="n">
-        <v>11.66</v>
+        <v>11.71</v>
       </c>
       <c r="M13" t="n">
         <v>1.75</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>11.31</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H14" t="n">
-        <v>454.25</v>
+        <v>440.75</v>
       </c>
       <c r="I14" t="n">
         <v>448.0607147373973</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.63</v>
+        <v>-10.37</v>
       </c>
       <c r="L14" t="n">
-        <v>9.369999999999999</v>
+        <v>10.72</v>
       </c>
       <c r="M14" t="n">
         <v>1.55</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>11.34</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45426</v>
+        <v>45427</v>
       </c>
       <c r="H15" t="n">
-        <v>454.85</v>
+        <v>483.65</v>
       </c>
       <c r="I15" t="n">
         <v>482.6689198218186</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.2</v>
+        <v>-9.73</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8</v>
+        <v>10.78</v>
       </c>
       <c r="M15" t="n">
         <v>1.97</v>
       </c>
       <c r="N15" t="n">
-        <v>4.41</v>
+        <v>6.33</v>
       </c>
       <c r="O15" t="n">
         <v>-2.97</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>12.87</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H16" t="n">
-        <v>521.55</v>
+        <v>453.25</v>
       </c>
       <c r="I16" t="n">
         <v>462.9351253976163</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>7.84</v>
+        <v>-6.29</v>
       </c>
       <c r="L16" t="n">
-        <v>5.8</v>
+        <v>11.11</v>
       </c>
       <c r="M16" t="n">
-        <v>0.58</v>
+        <v>1.46</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>13.1</v>
       </c>
       <c r="O16" t="n">
         <v>6.33</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>20.66</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45488</v>
+        <v>45489</v>
       </c>
       <c r="H17" t="n">
-        <v>518</v>
+        <v>541.5</v>
       </c>
       <c r="I17" t="n">
         <v>523.626563643916</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K17" t="n">
-        <v>-14.29</v>
+        <v>-19.47</v>
       </c>
       <c r="L17" t="n">
-        <v>16.94</v>
+        <v>20.49</v>
       </c>
       <c r="M17" t="n">
         <v>1.96</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>10.38</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45516</v>
+        <v>45517</v>
       </c>
       <c r="H18" t="n">
-        <v>524.9</v>
+        <v>502.5</v>
       </c>
       <c r="I18" t="n">
         <v>524.0439528227546</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.07</v>
+        <v>-7.2</v>
       </c>
       <c r="L18" t="n">
-        <v>5.76</v>
+        <v>7.97</v>
       </c>
       <c r="M18" t="n">
         <v>2.17</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>16.8</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="H19" t="n">
-        <v>458.55</v>
+        <v>481.45</v>
       </c>
       <c r="I19" t="n">
         <v>468.3501036243962</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K19" t="n">
-        <v>8.75</v>
+        <v>4.19</v>
       </c>
       <c r="L19" t="n">
         <v>6.46</v>
@@ -1524,7 +1751,7 @@
         <v>1.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.58</v>
+        <v>4.99</v>
       </c>
       <c r="O19" t="n">
         <v>-4.27</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="H20" t="n">
-        <v>451.35</v>
+        <v>449.45</v>
       </c>
       <c r="I20" t="n">
         <v>450.8780770836844</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.25</v>
+        <v>-6.65</v>
       </c>
       <c r="L20" t="n">
         <v>7.29</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.85</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H21" t="n">
-        <v>386.65</v>
+        <v>391.15</v>
       </c>
       <c r="I21" t="n">
         <v>386.7727643140349</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K21" t="n">
-        <v>13.97</v>
+        <v>12.97</v>
       </c>
       <c r="L21" t="n">
         <v>1.61</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.09</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="H22" t="n">
-        <v>450.65</v>
+        <v>447.7</v>
       </c>
       <c r="I22" t="n">
         <v>448.5250679419373</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K22" t="n">
-        <v>15.21</v>
+        <v>14.46</v>
       </c>
       <c r="L22" t="n">
         <v>7.22</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.07</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="H23" t="n">
-        <v>437.1</v>
+        <v>449.4</v>
       </c>
       <c r="I23" t="n">
         <v>445.8169096885842</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K23" t="n">
-        <v>2.37</v>
+        <v>-0.38</v>
       </c>
       <c r="L23" t="n">
         <v>2.12</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>6.3</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H24" t="n">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="I24" t="n">
         <v>423.6598814258307</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.43</v>
+        <v>-6.76</v>
       </c>
       <c r="L24" t="n">
-        <v>5.85</v>
+        <v>7.21</v>
       </c>
       <c r="M24" t="n">
         <v>0.41</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>5.74</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="H25" t="n">
-        <v>410.3</v>
+        <v>440.55</v>
       </c>
       <c r="I25" t="n">
         <v>413.5238240570727</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K25" t="n">
-        <v>2.08</v>
+        <v>-5.14</v>
       </c>
       <c r="L25" t="n">
-        <v>1.91</v>
+        <v>5.81</v>
       </c>
       <c r="M25" t="n">
         <v>2.59</v>
       </c>
       <c r="N25" t="n">
-        <v>4.5</v>
+        <v>7.37</v>
       </c>
       <c r="O25" t="n">
         <v>-1.41</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>10.26</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H26" t="n">
-        <v>411.35</v>
+        <v>404.5</v>
       </c>
       <c r="I26" t="n">
         <v>405.3888151578475</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.63</v>
+        <v>-8.18</v>
       </c>
       <c r="L26" t="n">
-        <v>8.82</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>2.99</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H27" t="n">
-        <v>392.6</v>
+        <v>411.45</v>
       </c>
       <c r="I27" t="n">
         <v>392.7361649015463</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K27" t="n">
-        <v>2.94</v>
+        <v>-1.72</v>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
         <v>4.94</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>10.44</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H28" t="n">
-        <v>428.5</v>
+        <v>391.3</v>
       </c>
       <c r="I28" t="n">
         <v>412.7162604443413</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K28" t="n">
-        <v>4.14</v>
+        <v>-4.9</v>
       </c>
       <c r="L28" t="n">
         <v>7.86</v>
       </c>
       <c r="M28" t="n">
-        <v>1.23</v>
+        <v>8.52</v>
       </c>
       <c r="N28" t="n">
-        <v>2.91</v>
+        <v>8.68</v>
       </c>
       <c r="O28" t="n">
         <v>4.8</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>9.49</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="H29" t="n">
-        <v>419</v>
+        <v>422.25</v>
       </c>
       <c r="I29" t="n">
         <v>420.7442194599891</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.08</v>
+        <v>-7.91</v>
       </c>
       <c r="L29" t="n">
-        <v>8.460000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="M29" t="n">
         <v>1.52</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>6.39</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H30" t="n">
-        <v>404.1</v>
+        <v>391.5</v>
       </c>
       <c r="I30" t="n">
         <v>397.4035267737071</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.3</v>
+        <v>-7.28</v>
       </c>
       <c r="L30" t="n">
-        <v>5.21</v>
+        <v>7.48</v>
       </c>
       <c r="M30" t="n">
         <v>0.95</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>3.12</v>
       </c>
       <c r="O30" t="n">
         <v>0.78</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2211,6 +2582,14 @@
       <c r="Q31" t="n">
         <v>30</v>
       </c>
+      <c r="R31" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4177,7 +4556,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.5</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="6">
@@ -4187,7 +4566,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -4197,7 +4576,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -4207,7 +4586,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -4217,7 +4596,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -4227,7 +4606,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109.2</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11">
@@ -4267,7 +4646,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="15">
@@ -4277,7 +4656,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.74</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="16">
@@ -4287,7 +4666,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.42</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="17">
@@ -4297,7 +4676,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45.54</v>
+        <v>34.27</v>
       </c>
     </row>
     <row r="18">
@@ -4307,7 +4686,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -4317,7 +4696,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.92</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="20">
@@ -4327,7 +4706,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.85</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="21">
@@ -4337,7 +4716,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.94</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="22">
@@ -4347,7 +4726,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -4357,7 +4736,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -4367,7 +4746,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="25">
@@ -4377,7 +4756,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.97</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="26">
@@ -4387,7 +4766,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.73</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="27">
@@ -4397,7 +4776,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.79</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="28">
@@ -4407,7 +4786,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
